--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486942_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486942_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5342</v>
+        <v>5.64</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8444</v>
+        <v>4.7209</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6898</v>
+        <v>0.9191</v>
       </c>
       <c r="G2" t="n">
         <v>1.8047</v>
@@ -610,13 +610,13 @@
         <v>2.4641</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9616</v>
+        <v>1.0674</v>
       </c>
       <c r="T2" t="n">
-        <v>1.929</v>
+        <v>0.8055</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0326</v>
+        <v>0.2619</v>
       </c>
       <c r="V2" t="n">
         <v>2.3573</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5348</v>
+        <v>1.6979</v>
       </c>
       <c r="E3" t="n">
-        <v>0.975</v>
+        <v>1.3159</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5598</v>
+        <v>0.3819</v>
       </c>
       <c r="G3" t="n">
         <v>2.2973</v>
@@ -688,13 +688,13 @@
         <v>2.0534</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4161</v>
+        <v>0.5792</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2903</v>
+        <v>0.6313</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1258</v>
+        <v>-0.0521</v>
       </c>
       <c r="V3" t="n">
         <v>-1.1786</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0127</v>
+        <v>-0.0391</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0702</v>
+        <v>0.7176</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0828</v>
+        <v>-0.7568</v>
       </c>
       <c r="G4" t="n">
         <v>-1.0156</v>
@@ -766,13 +766,13 @@
         <v>1.2321</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4691</v>
+        <v>0.4426</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5538</v>
+        <v>0.2013</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0847</v>
+        <v>0.2413</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6982</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. KANE</t>
+          <t>J. CARRASCO MARTIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1815</v>
+        <v>-1.0755</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.9399</v>
+        <v>-0.712</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7584</v>
+        <v>-0.3635</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.097</v>
+        <v>-0.5109</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7655999999999999</v>
+        <v>0.4022</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3314</v>
+        <v>-0.9131</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.2579</v>
+        <v>-0.619</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.2974</v>
+        <v>0.0389</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0395</v>
+        <v>-0.6579</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1609</v>
+        <v>0.108</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.3632</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3709</v>
+        <v>-0.2552</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2053</v>
+        <v>0.4107</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1208</v>
+        <v>0.2034</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1045</v>
+        <v>-0.093</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0163</v>
+        <v>0.2964</v>
       </c>
       <c r="V5" t="n">
+        <v>-1.1786</v>
+      </c>
+      <c r="W5" t="n">
         <v>0</v>
       </c>
-      <c r="W5" t="n">
-        <v>0.2402</v>
-      </c>
       <c r="X5" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. CARRASCO MARTIN</t>
+          <t>I. VALERA COROMINAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1866</v>
+        <v>-1.0889</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8824</v>
+        <v>-0.8048</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3042</v>
+        <v>-0.2841</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5109</v>
+        <v>-1.7349</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4022</v>
+        <v>-0.8693</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9131</v>
+        <v>-0.8656</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.619</v>
+        <v>-0.58</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0389</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6579</v>
+        <v>0.0395</v>
       </c>
       <c r="M6" t="n">
-        <v>0.108</v>
+        <v>-1.1549</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3632</v>
+        <v>-0.2498</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2552</v>
+        <v>-0.905</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0922</v>
+        <v>-0.1754</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2635</v>
+        <v>-0.2248</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3557</v>
+        <v>0.0494</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. VALERA COROMINAS</t>
+          <t>S. KANE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2231</v>
+        <v>-1.0951</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9094</v>
+        <v>-1.9127</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3137</v>
+        <v>0.8176</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7349</v>
+        <v>-1.097</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8693</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8656</v>
+        <v>-0.3314</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.58</v>
+        <v>-1.2579</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-1.2974</v>
       </c>
       <c r="L7" t="n">
         <v>0.0395</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1549</v>
+        <v>0.1609</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2498</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.905</v>
+        <v>-0.3709</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8214</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R7" t="n">
         <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3096</v>
+        <v>0.2073</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3294</v>
+        <v>0.1316</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0198</v>
+        <v>0.0756</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5621</v>
+        <v>-1.12</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0211</v>
+        <v>0.0061</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.541</v>
+        <v>-1.126</v>
       </c>
       <c r="G8" t="n">
         <v>-2.3256</v>
@@ -1078,13 +1078,13 @@
         <v>2.2588</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6882</v>
+        <v>-0.2461</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0346</v>
+        <v>0.0617</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7228</v>
+        <v>-0.3078</v>
       </c>
       <c r="V8" t="n">
         <v>-0.8070000000000001</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8876</v>
+        <v>-2.0079</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.4016</v>
+        <v>-3.4331</v>
       </c>
       <c r="F9" t="n">
-        <v>1.514</v>
+        <v>1.4251</v>
       </c>
       <c r="G9" t="n">
         <v>-1.038</v>
@@ -1156,13 +1156,13 @@
         <v>2.6694</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5436</v>
+        <v>0.3361</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7287</v>
+        <v>0.2399</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1851</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0.1314</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.9558</v>
+        <v>-6.8638</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.5824</v>
+        <v>-5.7572</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3734</v>
+        <v>-1.1066</v>
       </c>
       <c r="G10" t="n">
         <v>-5.1426</v>
@@ -1234,13 +1234,13 @@
         <v>1.6427</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3758</v>
+        <v>-0.2838</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.1088</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4418</v>
+        <v>-0.1751</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.940399999999999</v>
+        <v>-5.9524</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.847199999999999</v>
+        <v>-5.8593</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.09309999999999996</v>
+        <v>-0.09329999999999994</v>
       </c>
       <c r="G11" t="n">
         <v>-8.762599999999999</v>
@@ -1291,19 +1291,19 @@
         <v>3.426599999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.1993</v>
+        <v>-4.199299999999999</v>
       </c>
       <c r="M11" t="n">
         <v>-7.9901</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9282999999999998</v>
+        <v>-0.9282999999999999</v>
       </c>
       <c r="O11" t="n">
         <v>-7.061900000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>2.053599999999999</v>
+        <v>2.0536</v>
       </c>
       <c r="Q11" t="n">
         <v>-12.3204</v>
@@ -1312,19 +1312,19 @@
         <v>14.374</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1426</v>
+        <v>2.1307</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6566000000000002</v>
+        <v>1.6447</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4859999999999997</v>
+        <v>0.4857999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3737</v>
       </c>
       <c r="W11" t="n">
-        <v>5.5891</v>
+        <v>5.589100000000001</v>
       </c>
       <c r="X11" t="n">
         <v>-6.962700000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.9885</v>
+        <v>4.7567</v>
       </c>
       <c r="E12" t="n">
-        <v>5.3702</v>
+        <v>4.5334</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3817</v>
+        <v>0.2233</v>
       </c>
       <c r="G12" t="n">
         <v>3.7554</v>
@@ -1390,13 +1390,13 @@
         <v>1.6427</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.3129</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8405</v>
+        <v>0.0037</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9216</v>
+        <v>-0.3166</v>
       </c>
       <c r="V12" t="n">
         <v>0.6982</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.3818</v>
+        <v>4.5986</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0443</v>
+        <v>1.2996</v>
       </c>
       <c r="F13" t="n">
-        <v>3.3375</v>
+        <v>3.2991</v>
       </c>
       <c r="G13" t="n">
         <v>2.7245</v>
@@ -1468,13 +1468,13 @@
         <v>1.6427</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6569</v>
+        <v>0.5599</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.5073</v>
+        <v>-0.2521</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8504</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0.6982</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9324</v>
+        <v>3.1748</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8546</v>
+        <v>1.75</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0778</v>
+        <v>1.4248</v>
       </c>
       <c r="G14" t="n">
         <v>3.2125</v>
@@ -1546,13 +1546,13 @@
         <v>1.6427</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8961</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2249</v>
+        <v>-0.3295</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6713</v>
+        <v>-0.3243</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. MUÑOZ QUIÑONES</t>
+          <t>J. GONZALEZ ALBADALEJO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1939</v>
+        <v>2.4838</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4369</v>
+        <v>2.1284</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7569</v>
+        <v>0.3554</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5403</v>
+        <v>1.3925</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2165</v>
+        <v>-1.3855</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3238</v>
+        <v>2.7779</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5995</v>
+        <v>0.7306</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3233</v>
+        <v>-1.255</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2763</v>
+        <v>1.9856</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0592</v>
+        <v>0.6619</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1068</v>
+        <v>-0.1305</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0476</v>
+        <v>0.7924</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.8481</v>
+        <v>-0.616</v>
       </c>
       <c r="Q15" t="n">
         <v>-3.0801</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2321</v>
+        <v>2.4641</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9821</v>
+        <v>-0.6499</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6773</v>
+        <v>-0.2365</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3048</v>
+        <v>-0.4133</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.4805</v>
+        <v>2.3573</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2402</v>
+        <v>4.7145</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7207</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. MERLO</t>
+          <t>V. MUÑOZ QUIÑONES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5899</v>
+        <v>1.4128</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.4847</v>
+        <v>0.4955</v>
       </c>
       <c r="F16" t="n">
-        <v>4.0746</v>
+        <v>0.9173</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2247</v>
+        <v>2.5403</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.7746</v>
+        <v>1.2165</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5499</v>
+        <v>1.3238</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.292</v>
+        <v>2.5995</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.6993</v>
+        <v>2.3233</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4074</v>
+        <v>0.2763</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0672</v>
+        <v>-0.0592</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-1.1068</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1425</v>
+        <v>1.0476</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.8214</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q16" t="n">
         <v>-3.0801</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2588</v>
+        <v>1.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8762</v>
+        <v>1.201</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1126</v>
+        <v>0.7359</v>
       </c>
       <c r="U16" t="n">
-        <v>1.9888</v>
+        <v>0.4652</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2402</v>
+        <v>-0.4805</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2402</v>
+        <v>-0.7207</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GONZALEZ ALBADALEJO</t>
+          <t>S. MERLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5608</v>
+        <v>-0.2576</v>
       </c>
       <c r="E17" t="n">
-        <v>1.187</v>
+        <v>-3.4847</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6262</v>
+        <v>3.2271</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3925</v>
+        <v>-0.2247</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3855</v>
+        <v>-1.7746</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7779</v>
+        <v>1.5499</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7306</v>
+        <v>-0.292</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.255</v>
+        <v>-1.6993</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9856</v>
+        <v>1.4074</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6619</v>
+        <v>0.0672</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1305</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7924</v>
+        <v>0.1425</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.616</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q17" t="n">
         <v>-3.0801</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4641</v>
+        <v>2.2588</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.5729</v>
+        <v>1.0287</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.178</v>
+        <v>-0.1126</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.395</v>
+        <v>1.1414</v>
       </c>
       <c r="V17" t="n">
-        <v>2.3573</v>
+        <v>-0.2402</v>
       </c>
       <c r="W17" t="n">
-        <v>4.7145</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.3573</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9085</v>
+        <v>-1.5012</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1026</v>
+        <v>-1.8348</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1941</v>
+        <v>0.3336</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7992</v>
@@ -1858,13 +1858,13 @@
         <v>0.616</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2398</v>
+        <v>0.647</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0072</v>
+        <v>0.275</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2326</v>
+        <v>0.3721</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9384</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2118</v>
+        <v>-1.7097</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.842</v>
+        <v>-0.7373</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3698</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>0.2857</v>
@@ -1936,13 +1936,13 @@
         <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9554</v>
+        <v>-0.4533</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2635</v>
+        <v>-0.1589</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6919</v>
+        <v>-0.2944</v>
       </c>
       <c r="V19" t="n">
         <v>-0.7207</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.5866</v>
+        <v>-3.9258</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.3706</v>
+        <v>-4.0568</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2159</v>
+        <v>0.131</v>
       </c>
       <c r="G20" t="n">
         <v>-4.1243</v>
@@ -2014,13 +2014,13 @@
         <v>0.616</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0783</v>
+        <v>-0.4175</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7246</v>
+        <v>-0.4108</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3537</v>
+        <v>-0.0067</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,19 +2047,19 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>6.940400000000001</v>
+        <v>9.032399999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09309999999999974</v>
+        <v>0.09330000000000105</v>
       </c>
       <c r="F21" t="n">
-        <v>6.8473</v>
+        <v>8.939299999999999</v>
       </c>
       <c r="G21" t="n">
         <v>8.762700000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.4985</v>
+        <v>-2.498499999999999</v>
       </c>
       <c r="I21" t="n">
         <v>11.2611</v>
@@ -2074,7 +2074,7 @@
         <v>7.0619</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7726000000000004</v>
+        <v>0.7726000000000002</v>
       </c>
       <c r="N21" t="n">
         <v>-3.4268</v>
@@ -2092,19 +2092,19 @@
         <v>12.3204</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1426</v>
+        <v>0.9493000000000005</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4859000000000001</v>
+        <v>-0.4858000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6569</v>
+        <v>1.4354</v>
       </c>
       <c r="V21" t="n">
         <v>1.3739</v>
       </c>
       <c r="W21" t="n">
-        <v>6.9628</v>
+        <v>6.962800000000001</v>
       </c>
       <c r="X21" t="n">
         <v>-5.5892</v>
